--- a/data_extactor/batch_10_fa/trimmed/batch_0011_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0011_fa_trim.xlsx
@@ -508,12 +508,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مدیریت و امور اداری | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مدیریت و اداره | قانون و دولت | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران اعتباری | بازرسان و ارزیابان مالی | تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان صدور بیمه‌نامه (ارزیابان ریسک بیمه) | کارشناسان امور مقرراتی و تطبیق</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران اعتبارات و تسهیلات | بازرسان و ارزیابان مالی | تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان صدور بیمه‌نامه و ارزیابی ریسک | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,12 +565,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | اقتصاد و حسابداری | حقوق و مقررات دولتی | ریاضیات | مدیریت و امور اداری</t>
+          <t>زبان انگلیسی | اقتصاد و حسابداری | قانون و دولت | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | مدیران تطبیق و انطباق | تحلیل‌گران اعتباری | کارشناسان ریسک مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
+          <t>حسابداران و حسابرسان | تحلیل‌گران بودجه | مدیران تطبیق و نظارت مقرراتی | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان ریسک مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
+          <t>سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | امور اداری و دفتری | آموزش و تدریس | اقتصاد و حسابداری | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | آموزش و پرورش | اقتصاد و حسابداری | روان‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | توانایی کار با اعداد</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | توانایی عددی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مأموران وصول مطالبات و وصول چک | تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مصاحبه‌کنندگان و متصدیان پرونده‌های تسهیلاتی | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی شخصی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
+          <t>کارشناسان وصول مطالبات و پیگیری حساب‌ها | تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | کارشناسان پذیرش و امور اداری تسهیلات و وام | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | ریاضیات | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | حقوق و مقررات دولتی | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | اقتصاد و حسابداری | زبان انگلیسی | ریاضیات | فروش و بازاریابی | قانون و دولت | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تحلیل‌گران اعتباری | کارشناسان و متصدیان اعتبارسنجی و تأیید اعتبار | مشاوران اعتباری و مدیریت بدهی | مدیران مالی | مصاحبه‌کنندگان و متصدیان پرونده‌های تسهیلاتی | متصدیان افتتاح حساب | تحویل‌داران و متصدیان امور بانکی</t>
+          <t>تحلیل‌گران اعتبارات و تسهیلات | کارشناسان اعتبارسنجی، بررسی و تایید تسهیلات | مشاوران اعتباری و مدیریت بدهی | مدیران امور مالی | کارشناسان پذیرش و امور اداری تسهیلات و وام | متصدیان افتتاح حساب | تحویل‌داران و متصدیان امور بانکی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نگارش | نظارت | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | امور اداری و دفتری | حقوق و مقررات دولتی | اقتصاد و حسابداری | مدیریت و امور اداری</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | اداری | قانون و دولت | اقتصاد و حسابداری | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | مأموران وصول مطالبات و وصول چک | کارمندان دفترداری، حسابداری و حسابرسی | کارشناسان نظارت و تطبیق | تحلیل‌گران اعتباری | بازرسان و ارزیابان مالی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارشناسان وصول مطالبات و پیگیری حساب‌ها | کارمندان دفترداری، حسابداری و امور حسابرسی | کارشناسان پایش انطباق و بازرسی مقرراتی | تحلیل‌گران اعتبارات و تسهیلات | بازرسان و ارزیابان مالی | کارشناسان تنظیم و تسلیم اظهارنامه مالیاتی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | نگارش</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | ریاضیات | حقوق و مقررات دولتی | رایانه و الکترونیک | امور اداری و دفتری</t>
+          <t>اقتصاد و حسابداری | زبان انگلیسی | خدمات مشتری و شخصی | ریاضیات | قانون و دولت | رایانه و الکترونیک | اداری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | توانایی کار با اعداد | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | توانایی عددی | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و حسابرسی | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی شخصی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارمندان دفترداری، حسابداری و امور حسابرسی | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | کارشناسان و مسئولان تسهیلات و اعتبارات | مشاوران مالی فردی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم تجربی | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و امور اداری | رایانه و الکترونیک | حقوق و مقررات دولتی | خدمات مشتریان و خدمات فردی</t>
+          <t>اقتصاد و حسابداری | ریاضیات | مدیریت و اداره | رایانه و الکترونیک | قانون و دولت | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان ریسک مالی | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | حسابداران و حسابرسان | مدیران مالی</t>
+          <t>تحلیل‌گران کمّی مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان ریسک مالی | تحلیل‌گران بودجه | بازرسان و ارزیابان مالی | حسابداران و حسابرسان | مدیران امور مالی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | شنیدن فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
+          <t>ریاضیات | تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | سخن گفتن | نگارش | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>استدلال ریاضی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | توانایی کار با اعداد | استدلال استقرایی</t>
+          <t>استدلال ریاضی | درک کتبی | درک شفاهی | بیان کتبی | استدلال قیاسی | توانایی عددی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اکچوئریست‌ها (کارشناسان محاسبات فنی بیمه) | تحلیل‌گران هوش تجاری | دانشمندان داده | اقتصاددانان | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | متخصصان آمار</t>
+          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | تحلیل‌گران هوش تجاری | دانشمندان داده | اقتصاددانان | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,12 +964,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
+          <t>گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | درک مطلب | یادگیری فعال | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و امور اداری | ریاضیات | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | اقتصاد و حسابداری | رایانه و الکترونیک | مدیریت و اداره | ریاضیات | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>حسابداران و حسابرسان | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال (فورنزیک دیجیتال) | بازرسان و ارزیابان مالی | وکلا | کارآگاهان و بازرسان خصوصی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
+          <t>حسابداران و حسابرسان | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | بازرسان و ارزیابان مالی | وکلا | کارآگاهان و بازرسان خصوصی | ممیزان، ماموران وصول و کارشناسان مالیاتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | درک مطلب | تفکر انتقادی | شنیدن فعال | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
+          <t>سخن گفتن | درک مطلب | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | نظارت | نگارش | راهبردهای یادگیری | ریاضیات</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | ریاضیات | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | ریاضیات | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | مرتب‌سازی اطلاعات | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بیان شفاهی | ترتیب‌دهی اطلاعات | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>معماران شبکه‌های کامپیوتری | برنامه‌نویسان کامپیوتر | مهندسان و معماران سیستم‌های کامپیوتری | مدیران پایگاه داده (DBA) | تحلیل‌گران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | کارشناسان تضمین کیفیت و آزمون نرم‌افزار</t>
+          <t>معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران پایگاه داده | تحلیل‌گران امنیت اطلاعات | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
